--- a/etf_holdings/2026-09-30_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-30_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,52 +1458,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8028</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>昇陽半導體</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
+      <c r="J18" t="n">
+        <v>94000</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-29_00405A_full_holdings.xlsx</t>
+          <t>2026-09-29_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1518,100 +1518,82 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>110000</v>
+        <v>60000</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-29_00405A_full_holdings.xlsx</t>
+          <t>2026-09-29_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.97%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.68%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.29%</t>
-        </is>
-      </c>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>378000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>278000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
+        <v>41000</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-29_00405A_full_holdings.xlsx</t>
+          <t>2026-09-29_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1621,60 +1603,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>250000</v>
+        <v>83000</v>
       </c>
       <c r="K21" t="n">
-        <v>100000</v>
+        <v>166000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-150,000</t>
+          <t>83,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-29_00405A_full_holdings.xlsx</t>
+          <t>2026-09-29_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1684,186 +1666,150 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>LASERTEC CORP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>LASERTEC CORP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>110000</v>
+        <v>22600</v>
       </c>
       <c r="K22" t="n">
-        <v>80000</v>
+        <v>45400</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>22,800</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-29_00405A_full_holdings.xlsx</t>
+          <t>2026-09-29_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2.48%</t>
-        </is>
-      </c>
+          <t>昇陽半導體</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.90%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.58%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>322000</v>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>252000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-70,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-29_00407A_full_holdings.xlsx</t>
+          <t>2026-09-29_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.35%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.21%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>+0.86%</t>
-        </is>
-      </c>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>226000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>291000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>65,000</t>
-        </is>
-      </c>
+        <v>110000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-29_00407A_full_holdings.xlsx</t>
+          <t>2026-09-29_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1878,155 +1824,191 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>30900</v>
+        <v>378000</v>
       </c>
       <c r="K25" t="n">
-        <v>22900</v>
+        <v>278000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-29_00407A_full_holdings.xlsx</t>
+          <t>2026-09-29_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>250000</v>
+      </c>
       <c r="K26" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>100000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-150,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+          <t>2026-09-29_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>7734</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>印能科技</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>印能科技</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>110000</v>
+      </c>
       <c r="K27" t="n">
-        <v>241040</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>80000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+          <t>2026-09-29_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2039,74 +2021,110 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>2.48%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
       <c r="J28" t="n">
-        <v>227000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+        <v>322000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-70,000</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+          <t>2026-09-29_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>光聖</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
       <c r="J29" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+        <v>226000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>291000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>65,000</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+          <t>2026-09-29_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2116,53 +2134,53 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3627000</v>
+        <v>30900</v>
       </c>
       <c r="K30" t="n">
-        <v>4167000</v>
+        <v>22900</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>540,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+          <t>2026-09-29_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2174,55 +2192,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>3.82%</t>
-        </is>
-      </c>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.38%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>+0.56%</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>598000</v>
-      </c>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>669000</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>71,000</t>
-        </is>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>2026-09-29_00400A_full_holdings.xlsx</t>
@@ -2237,55 +2237,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>3.89%</t>
-        </is>
-      </c>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.82%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>+0.93%</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>227000</v>
-      </c>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>282000</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>55,000</t>
-        </is>
-      </c>
+        <v>241040</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>2026-09-29_00400A_full_holdings.xlsx</t>
@@ -2300,56 +2282,335 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>227000</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3627000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4167000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>540,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3.82%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>598000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>669000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>71,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3.89%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4.82%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+0.93%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>227000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>282000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-29_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>3665</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2.05%</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2.65%</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>+0.60%</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J38" t="n">
         <v>241000</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K38" t="n">
         <v>295000</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>54,000</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>2026-09-29_00400A_full_holdings.xlsx</t>
         </is>
